--- a/output/roomself_excel/13282.xlsx
+++ b/output/roomself_excel/13282.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>189952</v>
+        <v>92944</v>
       </c>
       <c r="D2" t="n">
-        <v>3532</v>
+        <v>2632</v>
       </c>
       <c r="E2" t="n">
-        <v>597</v>
+        <v>362</v>
       </c>
       <c r="F2" t="n">
-        <v>533</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28413</v>
+        <v>189952</v>
       </c>
       <c r="D3" t="n">
-        <v>1416</v>
+        <v>3532</v>
       </c>
       <c r="E3" t="n">
-        <v>152</v>
+        <v>597</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56920</v>
+        <v>28413</v>
       </c>
       <c r="D5" t="n">
-        <v>2212</v>
+        <v>1416</v>
       </c>
       <c r="E5" t="n">
-        <v>753</v>
+        <v>152</v>
       </c>
       <c r="F5" t="n">
-        <v>597</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92944</v>
+        <v>56920</v>
       </c>
       <c r="D6" t="n">
-        <v>2632</v>
+        <v>2212</v>
       </c>
       <c r="E6" t="n">
-        <v>362</v>
+        <v>229</v>
       </c>
       <c r="F6" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13282.xlsx
+++ b/output/roomself_excel/13282.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2632</v>
       </c>
-      <c r="E2" t="n">
-        <v>362</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>352</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>3532</v>
       </c>
-      <c r="E3" t="n">
-        <v>597</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>533</v>
+        <v>512</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>361</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>503</v>
+      </c>
+      <c r="M3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +600,31 @@
       <c r="D4" t="n">
         <v>2828</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>410</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>22</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>297</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +641,23 @@
       <c r="D5" t="n">
         <v>1416</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>152</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>22</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +674,31 @@
       <c r="D6" t="n">
         <v>2212</v>
       </c>
-      <c r="E6" t="n">
-        <v>229</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>204</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>207</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
